--- a/output/books.xlsx
+++ b/output/books.xlsx
@@ -442,10 +442,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
